--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1509,6 +1509,615 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128876631</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96221</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tovaberget - Bolum 15:1, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>420970</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6464652</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bolum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bondeskog</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128876187</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87024</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tovaberget - Bolum 15:1, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>421034</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6464586</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bolum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bondeskog</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128876630</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91272</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tovaberget - Bolum 15:1, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>420970</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6464652</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bolum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bondeskog</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128876176</v>
+      </c>
+      <c r="B12" t="n">
+        <v>86980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>449</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tovaberget - Bolum 15:1, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>421045</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6464703</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bolum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bondeskog</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128876184</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92196</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tovaberget - Bolum 15:1, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>421004</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6464580</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bolum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bondeskog</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128876192</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91272</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tovaberget - Bolum 15:1, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>421000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6464572</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bolum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bondeskog</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>128876631</v>
       </c>
       <c r="B9" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128876187</v>
       </c>
       <c r="B10" t="n">
-        <v>87024</v>
+        <v>87025</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128876630</v>
       </c>
       <c r="B11" t="n">
-        <v>91272</v>
+        <v>91277</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128876176</v>
       </c>
       <c r="B12" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128876184</v>
       </c>
       <c r="B13" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>128876192</v>
       </c>
       <c r="B14" t="n">
-        <v>91272</v>
+        <v>91277</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>128876631</v>
       </c>
       <c r="B9" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128876187</v>
       </c>
       <c r="B10" t="n">
-        <v>87025</v>
+        <v>87029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128876630</v>
       </c>
       <c r="B11" t="n">
-        <v>91277</v>
+        <v>91281</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128876176</v>
       </c>
       <c r="B12" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128876184</v>
       </c>
       <c r="B13" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>128876192</v>
       </c>
       <c r="B14" t="n">
-        <v>91277</v>
+        <v>91281</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>128876631</v>
       </c>
       <c r="B9" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128876187</v>
       </c>
       <c r="B10" t="n">
-        <v>87029</v>
+        <v>87034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128876630</v>
       </c>
       <c r="B11" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128876176</v>
       </c>
       <c r="B12" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128876184</v>
       </c>
       <c r="B13" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>128876192</v>
       </c>
       <c r="B14" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>128876631</v>
       </c>
       <c r="B9" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128876187</v>
       </c>
       <c r="B10" t="n">
-        <v>87041</v>
+        <v>87044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128876630</v>
       </c>
       <c r="B11" t="n">
-        <v>91293</v>
+        <v>91296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128876176</v>
       </c>
       <c r="B12" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128876184</v>
       </c>
       <c r="B13" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>128876192</v>
       </c>
       <c r="B14" t="n">
-        <v>91293</v>
+        <v>91296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>129104174</v>
       </c>
       <c r="B15" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>129104169</v>
       </c>
       <c r="B16" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>128876631</v>
       </c>
       <c r="B9" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128876187</v>
       </c>
       <c r="B10" t="n">
-        <v>87044</v>
+        <v>87047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128876630</v>
       </c>
       <c r="B11" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128876176</v>
       </c>
       <c r="B12" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128876184</v>
       </c>
       <c r="B13" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>128876192</v>
       </c>
       <c r="B14" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>129104174</v>
       </c>
       <c r="B15" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>129104169</v>
       </c>
       <c r="B16" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>128876631</v>
       </c>
       <c r="B9" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128876187</v>
       </c>
       <c r="B10" t="n">
-        <v>87047</v>
+        <v>87051</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128876630</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128876176</v>
       </c>
       <c r="B12" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128876184</v>
       </c>
       <c r="B13" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>128876192</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>129104174</v>
       </c>
       <c r="B15" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>129104169</v>
       </c>
       <c r="B16" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>128876631</v>
       </c>
       <c r="B9" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128876187</v>
       </c>
       <c r="B10" t="n">
-        <v>87051</v>
+        <v>87058</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128876630</v>
       </c>
       <c r="B11" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128876176</v>
       </c>
       <c r="B12" t="n">
-        <v>87007</v>
+        <v>87014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128876184</v>
       </c>
       <c r="B13" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>128876192</v>
       </c>
       <c r="B14" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>129104174</v>
       </c>
       <c r="B15" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>129104169</v>
       </c>
       <c r="B16" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>128876631</v>
       </c>
       <c r="B9" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128876187</v>
       </c>
       <c r="B10" t="n">
-        <v>87058</v>
+        <v>87060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128876630</v>
       </c>
       <c r="B11" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128876176</v>
       </c>
       <c r="B12" t="n">
-        <v>87014</v>
+        <v>87016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128876184</v>
       </c>
       <c r="B13" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>128876192</v>
       </c>
       <c r="B14" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>129104174</v>
       </c>
       <c r="B15" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>129104169</v>
       </c>
       <c r="B16" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>128876631</v>
       </c>
       <c r="B9" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1616,7 +1616,7 @@
         <v>128876187</v>
       </c>
       <c r="B10" t="n">
-        <v>87060</v>
+        <v>87061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1715,7 +1715,7 @@
         <v>128876630</v>
       </c>
       <c r="B11" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
         <v>128876176</v>
       </c>
       <c r="B12" t="n">
-        <v>87016</v>
+        <v>87017</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1919,7 +1919,7 @@
         <v>128876184</v>
       </c>
       <c r="B13" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2021,7 +2021,7 @@
         <v>128876192</v>
       </c>
       <c r="B14" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2123,7 +2123,7 @@
         <v>129104174</v>
       </c>
       <c r="B15" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>129104169</v>
       </c>
       <c r="B16" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>128876631</v>
       </c>
       <c r="B9" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1919,7 +1919,7 @@
         <v>128876184</v>
       </c>
       <c r="B13" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2123,7 +2123,7 @@
         <v>129104174</v>
       </c>
       <c r="B15" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>129104169</v>
       </c>
       <c r="B16" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>128876631</v>
       </c>
       <c r="B9" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>129104174</v>
       </c>
       <c r="B15" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>129104169</v>
       </c>
       <c r="B16" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>128876631</v>
       </c>
       <c r="B9" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128876187</v>
       </c>
       <c r="B10" t="n">
-        <v>87061</v>
+        <v>87064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128876630</v>
       </c>
       <c r="B11" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128876176</v>
       </c>
       <c r="B12" t="n">
-        <v>87017</v>
+        <v>87020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128876184</v>
       </c>
       <c r="B13" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>128876192</v>
       </c>
       <c r="B14" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>129104174</v>
       </c>
       <c r="B15" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>129104169</v>
       </c>
       <c r="B16" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2025 artfynd.xlsx
+++ b/artfynd/A 34590-2025 artfynd.xlsx
@@ -675,61 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112361895</v>
+        <v>128876176</v>
       </c>
       <c r="B2" t="n">
-        <v>89374</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5678</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kruskantarell</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus undulatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Campo &amp; Papetti</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bolum 15:1, skifte 5, Vg</t>
+          <t>Tovaberget - Bolum 15:1, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420922</v>
+        <v>421045</v>
       </c>
       <c r="R2" t="n">
-        <v>6464708</v>
+        <v>6464703</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bondeskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,39 +759,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Äldre bondeskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112361903</v>
+        <v>112361902</v>
       </c>
       <c r="B3" t="n">
-        <v>89790</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,31 +788,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Rosetticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Quél.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -918,42 +896,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112361886</v>
+        <v>112361903</v>
       </c>
       <c r="B4" t="n">
-        <v>90540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4787</v>
+        <v>1106</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -969,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420906</v>
+        <v>420938</v>
       </c>
       <c r="R4" t="n">
-        <v>6464763</v>
+        <v>6464700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,6 +993,11 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre bondeskog</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Göteborg-Herbarium GB</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1037,15 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112361894</v>
+        <v>128876631</v>
       </c>
       <c r="B5" t="n">
-        <v>89374</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,45 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5678</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kruskantarell</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus undulatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Campo &amp; Papetti</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bolum 15:1, skifte 5, Vg</t>
+          <t>Tovaberget - Bolum 15:1, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>420913</v>
+        <v>420970</v>
       </c>
       <c r="R5" t="n">
-        <v>6464727</v>
+        <v>6464652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,12 +1080,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bondeskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,39 +1099,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre bondeskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112361889</v>
+        <v>128876192</v>
       </c>
       <c r="B6" t="n">
-        <v>89374</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,45 +1128,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5678</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kruskantarell</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus undulatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Campo &amp; Papetti</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bolum 15:1, skifte 5, Vg</t>
+          <t>Tovaberget - Bolum 15:1, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>420911</v>
+        <v>421000</v>
       </c>
       <c r="R6" t="n">
-        <v>6464732</v>
+        <v>6464572</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,12 +1182,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bondeskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,90 +1201,63 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Äldre bondeskog</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Göteborg-Herbarium GB</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112361902</v>
+        <v>128876630</v>
       </c>
       <c r="B7" t="n">
-        <v>89808</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1100</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosetticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Postia floriformis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Quél.) Jülich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bolum 15:1, skifte 5, Vg</t>
+          <t>Tovaberget - Bolum 15:1, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>420938</v>
+        <v>420970</v>
       </c>
       <c r="R7" t="n">
-        <v>6464700</v>
+        <v>6464652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,12 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bondeskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,44 +1303,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre bondeskog</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Göteborg-Herbarium GB</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112361888</v>
+        <v>128876184</v>
       </c>
       <c r="B8" t="n">
-        <v>88257</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,34 +1332,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6292</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bolum 15:1, skifte 5, Vg</t>
+          <t>Tovaberget - Bolum 15:1, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>420911</v>
+        <v>421004</v>
       </c>
       <c r="R8" t="n">
-        <v>6464732</v>
+        <v>6464580</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,12 +1386,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bondeskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,31 +1407,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre bondeskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128876631</v>
+        <v>128876187</v>
       </c>
       <c r="B9" t="n">
-        <v>96306</v>
+        <v>87412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,23 +1434,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>3624</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1546,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420970</v>
+        <v>421034</v>
       </c>
       <c r="R9" t="n">
-        <v>6464652</v>
+        <v>6464586</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,6 +1503,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1613,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128876187</v>
+        <v>112361886</v>
       </c>
       <c r="B10" t="n">
-        <v>87064</v>
+        <v>92886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,30 +1533,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3624</v>
+        <v>4787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Lactarius zonarioides</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tovaberget - Bolum 15:1, Vg</t>
+          <t>Bolum 15:1, skifte 5, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421034</v>
+        <v>420906</v>
       </c>
       <c r="R10" t="n">
-        <v>6464586</v>
+        <v>6464763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,17 +1598,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bondeskog</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,25 +1616,30 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre bondeskog</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128876630</v>
+        <v>112361889</v>
       </c>
       <c r="B11" t="n">
-        <v>91316</v>
+        <v>91683</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,34 +1647,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3215</v>
+        <v>5678</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kruskantarell</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Craterellus undulatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) E.Campo &amp; Papetti</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tovaberget - Bolum 15:1, Vg</t>
+          <t>Bolum 15:1, skifte 5, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>420970</v>
+        <v>420911</v>
       </c>
       <c r="R11" t="n">
-        <v>6464652</v>
+        <v>6464732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,17 +1712,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Bondeskog</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,63 +1726,85 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre bondeskog</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Göteborg-Herbarium GB</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128876176</v>
+        <v>112361894</v>
       </c>
       <c r="B12" t="n">
-        <v>87020</v>
+        <v>91683</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>449</v>
+        <v>5678</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kruskantarell</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Craterellus undulatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.) E.Campo &amp; Papetti</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tovaberget - Bolum 15:1, Vg</t>
+          <t>Bolum 15:1, skifte 5, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421045</v>
+        <v>420913</v>
       </c>
       <c r="R12" t="n">
-        <v>6464703</v>
+        <v>6464727</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,17 +1831,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Bondeskog</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,28 +1845,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre bondeskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128876184</v>
+        <v>112361895</v>
       </c>
       <c r="B13" t="n">
-        <v>92261</v>
+        <v>91683</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,34 +1880,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>5678</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kruskantarell</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Craterellus undulatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) E.Campo &amp; Papetti</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tovaberget - Bolum 15:1, Vg</t>
+          <t>Bolum 15:1, skifte 5, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421004</v>
+        <v>420922</v>
       </c>
       <c r="R13" t="n">
-        <v>6464580</v>
+        <v>6464708</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,17 +1945,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bondeskog</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,28 +1959,34 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre bondeskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128876192</v>
+        <v>112361888</v>
       </c>
       <c r="B14" t="n">
-        <v>91316</v>
+        <v>90721</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,34 +1994,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>6292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tovaberget - Bolum 15:1, Vg</t>
+          <t>Bolum 15:1, skifte 5, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421000</v>
+        <v>420911</v>
       </c>
       <c r="R14" t="n">
-        <v>6464572</v>
+        <v>6464732</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,17 +2048,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bondeskog</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,16 +2064,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre bondeskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2123,7 +2088,7 @@
         <v>129104174</v>
       </c>
       <c r="B15" t="n">
-        <v>97598</v>
+        <v>97983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2194,7 @@
         <v>129104169</v>
       </c>
       <c r="B16" t="n">
-        <v>100916</v>
+        <v>101325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
